--- a/tests/xyz/Example_AEM/Example_output_files/PSD_Plot.xlsx
+++ b/tests/xyz/Example_AEM/Example_output_files/PSD_Plot.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42c400a6d2268350/Penn/GitHub/PrO-VAT/tests/xyz/Example_AEM/Example_output_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42c400a6d2268350/Penn/GitHub/PARSE/tests/xyz/Example_AEM/Example_output_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="8_{7149973D-7FBA-47E4-9186-8284705DD2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F500B793-F5D7-4F9A-ADED-27124416D7B2}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="8_{7149973D-7FBA-47E4-9186-8284705DD2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B9AE340-FC4C-4184-AA84-FFDCE4513C73}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D12CB501-9D5F-4141-A117-3B2D7216ADD7}"/>
   </bookViews>
@@ -279,79 +279,79 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.97941999999999996</c:v>
+                  <c:v>0.95401999999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.93708999999999998</c:v>
+                  <c:v>0.89559999999999995</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.87170999999999998</c:v>
+                  <c:v>0.84289999999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.82723999999999998</c:v>
+                  <c:v>0.79661999999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.77893000000000001</c:v>
+                  <c:v>0.75822000000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.74697000000000002</c:v>
+                  <c:v>0.69865999999999995</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.67017000000000004</c:v>
+                  <c:v>0.63617000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.60094999999999998</c:v>
+                  <c:v>0.54488999999999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.50946000000000002</c:v>
+                  <c:v>0.46159</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.43325000000000002</c:v>
+                  <c:v>0.39573999999999998</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.36978</c:v>
+                  <c:v>0.33395000000000002</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.31402000000000002</c:v>
+                  <c:v>0.27622000000000002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.25059999999999999</c:v>
+                  <c:v>0.21653</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.19200999999999999</c:v>
+                  <c:v>0.16369</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.14224000000000001</c:v>
+                  <c:v>0.11602</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>9.9930000000000005E-2</c:v>
+                  <c:v>7.9619999999999996E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6.9159999999999999E-2</c:v>
+                  <c:v>5.2650000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.3459999999999999E-2</c:v>
+                  <c:v>3.329E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2.7660000000000001E-2</c:v>
+                  <c:v>2.0129999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.77E-2</c:v>
+                  <c:v>1.473E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.32E-2</c:v>
+                  <c:v>1.0070000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>8.94E-3</c:v>
+                  <c:v>5.77E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4.8300000000000001E-3</c:v>
+                  <c:v>3.8400000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2.0100000000000001E-3</c:v>
+                  <c:v>1.1800000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.1800000000000001E-3</c:v>
+                  <c:v>1.0499999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0</c:v>
@@ -536,82 +536,82 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.82320000000000282</c:v>
+                  <c:v>1.8392000000000033</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.6931999999999976</c:v>
+                  <c:v>2.3367999999999989</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.6151999999999975</c:v>
+                  <c:v>2.107999999999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.7787999999999988</c:v>
+                  <c:v>1.851199999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.9323999999999968</c:v>
+                  <c:v>1.5359999999999983</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.2784000000000013</c:v>
+                  <c:v>2.3824000000000054</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.0719999999999965</c:v>
+                  <c:v>2.4995999999999952</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.7688000000000059</c:v>
+                  <c:v>3.651200000000006</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.6595999999999953</c:v>
+                  <c:v>3.3319999999999963</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.0483999999999973</c:v>
+                  <c:v>2.6339999999999986</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.5387999999999988</c:v>
+                  <c:v>2.471599999999996</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.230400000000007</c:v>
+                  <c:v>2.3092000000000081</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.5367999999999991</c:v>
+                  <c:v>2.3875999999999986</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.3435999999999981</c:v>
+                  <c:v>2.1135999999999981</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.9907999999999975</c:v>
+                  <c:v>1.9067999999999985</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.6923999999999986</c:v>
+                  <c:v>1.4559999999999989</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.2308000000000046</c:v>
+                  <c:v>1.0788000000000035</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.0279999999999991</c:v>
+                  <c:v>0.77439999999999942</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.63199999999999934</c:v>
+                  <c:v>0.52639999999999965</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.39839999999999964</c:v>
+                  <c:v>0.21599999999999975</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.17999999999999985</c:v>
+                  <c:v>0.18639999999999982</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.17040000000000061</c:v>
+                  <c:v>0.17200000000000065</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.16439999999999985</c:v>
+                  <c:v>7.7199999999999921E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.1127999999999999</c:v>
+                  <c:v>0.10639999999999991</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>3.3199999999999973E-2</c:v>
+                  <c:v>5.2000000000000006E-3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4.7199999999999957E-2</c:v>
+                  <c:v>4.1999999999999961E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0</c:v>
@@ -1246,82 +1246,82 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.82320000000000282</c:v>
+                  <c:v>1.8392000000000033</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.6931999999999976</c:v>
+                  <c:v>2.3367999999999989</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.6151999999999975</c:v>
+                  <c:v>2.107999999999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.7787999999999988</c:v>
+                  <c:v>1.851199999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.9323999999999968</c:v>
+                  <c:v>1.5359999999999983</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.2784000000000013</c:v>
+                  <c:v>2.3824000000000054</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.0719999999999965</c:v>
+                  <c:v>2.4995999999999952</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.7688000000000059</c:v>
+                  <c:v>3.651200000000006</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.6595999999999953</c:v>
+                  <c:v>3.3319999999999963</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.0483999999999973</c:v>
+                  <c:v>2.6339999999999986</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.5387999999999988</c:v>
+                  <c:v>2.471599999999996</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.230400000000007</c:v>
+                  <c:v>2.3092000000000081</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.5367999999999991</c:v>
+                  <c:v>2.3875999999999986</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.3435999999999981</c:v>
+                  <c:v>2.1135999999999981</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.9907999999999975</c:v>
+                  <c:v>1.9067999999999985</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.6923999999999986</c:v>
+                  <c:v>1.4559999999999989</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.2308000000000046</c:v>
+                  <c:v>1.0788000000000035</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.0279999999999991</c:v>
+                  <c:v>0.77439999999999942</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.63199999999999934</c:v>
+                  <c:v>0.52639999999999965</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.39839999999999964</c:v>
+                  <c:v>0.21599999999999975</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.17999999999999985</c:v>
+                  <c:v>0.18639999999999982</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.17040000000000061</c:v>
+                  <c:v>0.17200000000000065</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.16439999999999985</c:v>
+                  <c:v>7.7199999999999921E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.1127999999999999</c:v>
+                  <c:v>0.10639999999999991</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>3.3199999999999973E-2</c:v>
+                  <c:v>5.2000000000000006E-3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4.7199999999999957E-2</c:v>
+                  <c:v>4.1999999999999961E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0</c:v>
@@ -3168,10 +3168,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3588,11 +3584,11 @@
         <v>0.33999999999999997</v>
       </c>
       <c r="C4">
-        <v>0.97941999999999996</v>
+        <v>0.95401999999999998</v>
       </c>
       <c r="D4">
         <f t="shared" ref="D4:D31" si="2">(C3-C4)/(B4-B3)</f>
-        <v>0.82320000000000282</v>
+        <v>1.8392000000000033</v>
       </c>
       <c r="F4">
         <v>0.5</v>
@@ -3618,11 +3614,11 @@
         <v>0.36499999999999999</v>
       </c>
       <c r="C5">
-        <v>0.93708999999999998</v>
+        <v>0.89559999999999995</v>
       </c>
       <c r="D5">
         <f t="shared" si="2"/>
-        <v>1.6931999999999976</v>
+        <v>2.3367999999999989</v>
       </c>
       <c r="F5">
         <v>0.75</v>
@@ -3648,11 +3644,11 @@
         <v>0.39</v>
       </c>
       <c r="C6">
-        <v>0.87170999999999998</v>
+        <v>0.84289999999999998</v>
       </c>
       <c r="D6">
         <f t="shared" si="2"/>
-        <v>2.6151999999999975</v>
+        <v>2.107999999999997</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -3678,11 +3674,11 @@
         <v>0.41500000000000004</v>
       </c>
       <c r="C7">
-        <v>0.82723999999999998</v>
+        <v>0.79661999999999999</v>
       </c>
       <c r="D7">
         <f t="shared" si="2"/>
-        <v>1.7787999999999988</v>
+        <v>1.851199999999998</v>
       </c>
       <c r="F7">
         <v>1.25</v>
@@ -3708,11 +3704,11 @@
         <v>0.44000000000000006</v>
       </c>
       <c r="C8">
-        <v>0.77893000000000001</v>
+        <v>0.75822000000000001</v>
       </c>
       <c r="D8">
         <f t="shared" si="2"/>
-        <v>1.9323999999999968</v>
+        <v>1.5359999999999983</v>
       </c>
       <c r="F8">
         <v>1.5</v>
@@ -3738,11 +3734,11 @@
         <v>0.46500000000000002</v>
       </c>
       <c r="C9">
-        <v>0.74697000000000002</v>
+        <v>0.69865999999999995</v>
       </c>
       <c r="D9">
         <f t="shared" si="2"/>
-        <v>1.2784000000000013</v>
+        <v>2.3824000000000054</v>
       </c>
       <c r="F9">
         <v>1.75</v>
@@ -3768,11 +3764,11 @@
         <v>0.49000000000000005</v>
       </c>
       <c r="C10">
-        <v>0.67017000000000004</v>
+        <v>0.63617000000000001</v>
       </c>
       <c r="D10">
         <f t="shared" si="2"/>
-        <v>3.0719999999999965</v>
+        <v>2.4995999999999952</v>
       </c>
       <c r="F10">
         <v>2</v>
@@ -3798,11 +3794,11 @@
         <v>0.51500000000000001</v>
       </c>
       <c r="C11">
-        <v>0.60094999999999998</v>
+        <v>0.54488999999999999</v>
       </c>
       <c r="D11">
         <f t="shared" si="2"/>
-        <v>2.7688000000000059</v>
+        <v>3.651200000000006</v>
       </c>
       <c r="F11">
         <v>2.25</v>
@@ -3828,11 +3824,11 @@
         <v>0.54</v>
       </c>
       <c r="C12">
-        <v>0.50946000000000002</v>
+        <v>0.46159</v>
       </c>
       <c r="D12">
         <f t="shared" si="2"/>
-        <v>3.6595999999999953</v>
+        <v>3.3319999999999963</v>
       </c>
       <c r="F12">
         <v>2.5</v>
@@ -3858,11 +3854,11 @@
         <v>0.56500000000000006</v>
       </c>
       <c r="C13">
-        <v>0.43325000000000002</v>
+        <v>0.39573999999999998</v>
       </c>
       <c r="D13">
         <f t="shared" si="2"/>
-        <v>3.0483999999999973</v>
+        <v>2.6339999999999986</v>
       </c>
       <c r="F13">
         <v>2.75</v>
@@ -3888,11 +3884,11 @@
         <v>0.59000000000000008</v>
       </c>
       <c r="C14">
-        <v>0.36978</v>
+        <v>0.33395000000000002</v>
       </c>
       <c r="D14">
         <f t="shared" si="2"/>
-        <v>2.5387999999999988</v>
+        <v>2.471599999999996</v>
       </c>
       <c r="F14">
         <v>3</v>
@@ -3918,11 +3914,11 @@
         <v>0.61499999999999999</v>
       </c>
       <c r="C15">
-        <v>0.31402000000000002</v>
+        <v>0.27622000000000002</v>
       </c>
       <c r="D15">
         <f t="shared" si="2"/>
-        <v>2.230400000000007</v>
+        <v>2.3092000000000081</v>
       </c>
       <c r="F15">
         <v>3.25</v>
@@ -3948,11 +3944,11 @@
         <v>0.64</v>
       </c>
       <c r="C16">
-        <v>0.25059999999999999</v>
+        <v>0.21653</v>
       </c>
       <c r="D16">
         <f t="shared" si="2"/>
-        <v>2.5367999999999991</v>
+        <v>2.3875999999999986</v>
       </c>
       <c r="F16">
         <v>3.5</v>
@@ -3978,11 +3974,11 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="C17">
-        <v>0.19200999999999999</v>
+        <v>0.16369</v>
       </c>
       <c r="D17">
         <f t="shared" si="2"/>
-        <v>2.3435999999999981</v>
+        <v>2.1135999999999981</v>
       </c>
       <c r="F17">
         <v>3.75</v>
@@ -4008,11 +4004,11 @@
         <v>0.69000000000000006</v>
       </c>
       <c r="C18">
-        <v>0.14224000000000001</v>
+        <v>0.11602</v>
       </c>
       <c r="D18">
         <f t="shared" si="2"/>
-        <v>1.9907999999999975</v>
+        <v>1.9067999999999985</v>
       </c>
       <c r="F18">
         <v>4</v>
@@ -4038,11 +4034,11 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="C19">
-        <v>9.9930000000000005E-2</v>
+        <v>7.9619999999999996E-2</v>
       </c>
       <c r="D19">
         <f t="shared" si="2"/>
-        <v>1.6923999999999986</v>
+        <v>1.4559999999999989</v>
       </c>
       <c r="F19">
         <v>4.25</v>
@@ -4068,11 +4064,11 @@
         <v>0.74</v>
       </c>
       <c r="C20">
-        <v>6.9159999999999999E-2</v>
+        <v>5.2650000000000002E-2</v>
       </c>
       <c r="D20">
         <f t="shared" si="2"/>
-        <v>1.2308000000000046</v>
+        <v>1.0788000000000035</v>
       </c>
       <c r="F20">
         <v>4.5</v>
@@ -4098,11 +4094,11 @@
         <v>0.76500000000000001</v>
       </c>
       <c r="C21">
-        <v>4.3459999999999999E-2</v>
+        <v>3.329E-2</v>
       </c>
       <c r="D21">
         <f t="shared" si="2"/>
-        <v>1.0279999999999991</v>
+        <v>0.77439999999999942</v>
       </c>
       <c r="F21">
         <v>4.75</v>
@@ -4128,11 +4124,11 @@
         <v>0.79</v>
       </c>
       <c r="C22">
-        <v>2.7660000000000001E-2</v>
+        <v>2.0129999999999999E-2</v>
       </c>
       <c r="D22">
         <f t="shared" si="2"/>
-        <v>0.63199999999999934</v>
+        <v>0.52639999999999965</v>
       </c>
       <c r="F22">
         <v>5</v>
@@ -4158,11 +4154,11 @@
         <v>0.81500000000000006</v>
       </c>
       <c r="C23">
-        <v>1.77E-2</v>
+        <v>1.473E-2</v>
       </c>
       <c r="D23">
         <f t="shared" si="2"/>
-        <v>0.39839999999999964</v>
+        <v>0.21599999999999975</v>
       </c>
       <c r="F23">
         <v>5.25</v>
@@ -4188,11 +4184,11 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="C24">
-        <v>1.32E-2</v>
+        <v>1.0070000000000001E-2</v>
       </c>
       <c r="D24">
         <f t="shared" si="2"/>
-        <v>0.17999999999999985</v>
+        <v>0.18639999999999982</v>
       </c>
       <c r="F24">
         <v>5.5</v>
@@ -4218,11 +4214,11 @@
         <v>0.86499999999999999</v>
       </c>
       <c r="C25">
-        <v>8.94E-3</v>
+        <v>5.77E-3</v>
       </c>
       <c r="D25">
         <f t="shared" si="2"/>
-        <v>0.17040000000000061</v>
+        <v>0.17200000000000065</v>
       </c>
       <c r="F25">
         <v>5.75</v>
@@ -4248,11 +4244,11 @@
         <v>0.89</v>
       </c>
       <c r="C26">
-        <v>4.8300000000000001E-3</v>
+        <v>3.8400000000000001E-3</v>
       </c>
       <c r="D26">
         <f t="shared" si="2"/>
-        <v>0.16439999999999985</v>
+        <v>7.7199999999999921E-2</v>
       </c>
       <c r="F26">
         <v>6</v>
@@ -4278,11 +4274,11 @@
         <v>0.91500000000000004</v>
       </c>
       <c r="C27">
-        <v>2.0100000000000001E-3</v>
+        <v>1.1800000000000001E-3</v>
       </c>
       <c r="D27">
         <f t="shared" si="2"/>
-        <v>0.1127999999999999</v>
+        <v>0.10639999999999991</v>
       </c>
       <c r="F27">
         <v>6.25</v>
@@ -4308,11 +4304,11 @@
         <v>0.94000000000000006</v>
       </c>
       <c r="C28">
-        <v>1.1800000000000001E-3</v>
+        <v>1.0499999999999999E-3</v>
       </c>
       <c r="D28">
         <f t="shared" si="2"/>
-        <v>3.3199999999999973E-2</v>
+        <v>5.2000000000000006E-3</v>
       </c>
       <c r="F28">
         <v>6.5</v>
@@ -4342,7 +4338,7 @@
       </c>
       <c r="D29">
         <f t="shared" si="2"/>
-        <v>4.7199999999999957E-2</v>
+        <v>4.1999999999999961E-2</v>
       </c>
       <c r="F29">
         <v>6.75</v>
